--- a/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
+++ b/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -254,13 +254,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,7 +736,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -741,7 +744,7 @@
 sales@hair-brushes.com    lucky@jsiu.com</t>
         </is>
       </c>
-      <c r="H1" s="28" t="n"/>
+      <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -867,28 +870,28 @@
       <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>ZW-YI7D-KWFL</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>老款细针洗头刷TPEE，硬度55，注意控制针头毛边，顶部印白色logo，颜色2404C绿色</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="29" t="n">
         <v>1.75</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="29">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>纸盒4800单支装</t>
         </is>
@@ -896,23 +899,23 @@
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="19" t="n"/>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="19" t="n"/>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">

--- a/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
+++ b/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年10月09日</t>
+          <t>2025年10月21日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>李万祥</t>
+          <t>多多</t>
         </is>
       </c>
       <c r="C5" s="16" t="n"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月23日</t>
+          <t>2025年12月05日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>

--- a/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
+++ b/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="14">
     <font>
       <name val="Arial"/>
       <charset val="134"/>
@@ -37,12 +37,6 @@
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
       <sz val="22"/>
     </font>
     <font>
@@ -53,12 +47,6 @@
     <font>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
       <sz val="12"/>
     </font>
     <font>
@@ -87,38 +75,12 @@
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-      <family val="2"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <family val="2"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="20"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -184,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,34 +167,34 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,26 +206,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -353,7 +316,7 @@
     <ext cx="1266825" cy="1266825"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
@@ -363,7 +326,12 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -721,22 +689,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="15.140625" customWidth="1" style="7" min="1" max="1"/>
-    <col width="44.5703125" customWidth="1" style="7" min="2" max="2"/>
-    <col width="35.85546875" customWidth="1" style="7" min="3" max="3"/>
-    <col width="11.7109375" customWidth="1" style="7" min="4" max="4"/>
-    <col width="9.42578125" customWidth="1" style="7" min="5" max="5"/>
-    <col width="20.7109375" customWidth="1" style="7" min="6" max="6"/>
-    <col width="25.7109375" customWidth="1" style="7" min="7" max="7"/>
-    <col width="17.28515625" customWidth="1" style="7" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="7" min="9" max="16384"/>
+    <col width="15.140625" customWidth="1" style="29" min="1" max="1"/>
+    <col width="44.5703125" customWidth="1" style="29" min="2" max="2"/>
+    <col width="35.85546875" customWidth="1" style="29" min="3" max="3"/>
+    <col width="11.7109375" customWidth="1" style="29" min="4" max="4"/>
+    <col width="9.42578125" customWidth="1" style="29" min="5" max="5"/>
+    <col width="20.7109375" customWidth="1" style="29" min="6" max="6"/>
+    <col width="25.7109375" customWidth="1" style="29" min="7" max="7"/>
+    <col width="17.28515625" customWidth="1" style="29" min="8" max="8"/>
+    <col width="9.140625" customWidth="1" style="29" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" style="29" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="86.25" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>宁波品秀美容科技有限公司
 宁波高新区江南路1528号高新科技广场2号楼10楼
@@ -747,7 +716,7 @@
       <c r="H1" s="26" t="n"/>
     </row>
     <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>订单</t>
         </is>
@@ -869,29 +838,29 @@
       </c>
       <c r="H6" s="20" t="n"/>
     </row>
-    <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
-      <c r="A7" s="29" t="inlineStr">
+    <row r="7" ht="99.95" customFormat="1" customHeight="1" s="2">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>ZW-YI7D-KWFL</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>老款细针洗头刷TPEE，硬度55，注意控制针头毛边，顶部印白色logo，颜色2404C绿色</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="27" t="n">
         <v>1.75</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="27">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>纸盒4800单支装</t>
         </is>
@@ -899,23 +868,23 @@
       <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="27" t="n"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1000,7 +969,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年12月05日</t>
+          <t>45天</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1011,7 +980,7 @@
           <t>[色卡图片未找到] logo 设计稿参照pdf附件</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr"/>
+      <c r="G14" s="25" t="n"/>
       <c r="H14" s="25" t="n"/>
     </row>
     <row r="15" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1028,8 +997,8 @@
       <c r="C15" s="25" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="inlineStr"/>
-      <c r="G15" s="25" t="inlineStr"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
       <c r="H15" s="25" t="n"/>
     </row>
     <row r="16" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1046,8 +1015,8 @@
       <c r="C16" s="25" t="n"/>
       <c r="D16" s="25" t="n"/>
       <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="inlineStr"/>
-      <c r="G16" s="25" t="inlineStr"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
       <c r="H16" s="25" t="n"/>
     </row>
     <row r="17" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1056,12 +1025,12 @@
           <t>出货样:</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr"/>
+      <c r="B17" s="25" t="n"/>
       <c r="C17" s="25" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="inlineStr"/>
-      <c r="G17" s="25" t="inlineStr"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
       <c r="H17" s="25" t="n"/>
     </row>
     <row r="18" ht="17.25" customFormat="1" customHeight="1" s="3">
@@ -1074,8 +1043,8 @@
       <c r="C18" s="25" t="n"/>
       <c r="D18" s="25" t="n"/>
       <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="inlineStr"/>
-      <c r="G18" s="25" t="inlineStr"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
       <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
@@ -1179,7 +1148,7 @@
       <c r="I25" s="5" t="n"/>
     </row>
     <row r="26" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A26" s="25" t="inlineStr"/>
+      <c r="A26" s="25" t="n"/>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="25" t="n"/>
       <c r="D26" s="25" t="n"/>
@@ -1189,7 +1158,7 @@
       <c r="H26" s="25" t="n"/>
     </row>
     <row r="27" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A27" s="25" t="inlineStr"/>
+      <c r="A27" s="25" t="n"/>
       <c r="B27" s="25" t="n"/>
       <c r="C27" s="25" t="n"/>
       <c r="D27" s="25" t="n"/>
@@ -1199,7 +1168,7 @@
       <c r="H27" s="25" t="n"/>
     </row>
     <row r="28" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A28" s="25" t="inlineStr"/>
+      <c r="A28" s="25" t="n"/>
       <c r="B28" s="25" t="n"/>
       <c r="C28" s="25" t="n"/>
       <c r="D28" s="25" t="n"/>
@@ -1209,7 +1178,7 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A29" s="25" t="inlineStr"/>
+      <c r="A29" s="25" t="n"/>
       <c r="B29" s="25" t="n"/>
       <c r="C29" s="25" t="n"/>
       <c r="D29" s="25" t="n"/>
@@ -1219,7 +1188,7 @@
       <c r="H29" s="25" t="n"/>
     </row>
     <row r="30" ht="17.25" customFormat="1" customHeight="1" s="5">
-      <c r="A30" s="25" t="inlineStr"/>
+      <c r="A30" s="25" t="n"/>
       <c r="B30" s="25" t="n"/>
       <c r="C30" s="25" t="n"/>
       <c r="D30" s="25" t="n"/>
@@ -1261,16 +1230,9 @@
     <row r="34" ht="21" customFormat="1" customHeight="1" s="6">
       <c r="H34" s="14" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="H38" s="14" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="12" t="n"/>
@@ -1371,7 +1333,6 @@
       <c r="A67" s="10" t="n"/>
       <c r="B67" s="12" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="17.25" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
@@ -1403,26 +1364,9 @@
       </c>
       <c r="F70" s="13" t="n"/>
     </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="H80" s="14" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>

--- a/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
+++ b/order_generation/PO_excel/ZW-YI7D-KWFL.xlsx
@@ -1078,7 +1078,7 @@
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>3）硬度按照55</t>
+          <t>3）硬度按照55(伟氏硬度计D型测值65+-0.8)(伟氏硬度计D型测值65+-0.8)</t>
         </is>
       </c>
       <c r="B21" s="25" t="n"/>
